--- a/Dia1.xlsx
+++ b/Dia1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alpf0069\Documents\Proyectos\Area TI\Fichas Tecnicas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C727D04-A9F2-480F-8F0F-AD57DFC4AF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3068F007-06A7-4CBE-842B-C59244131199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,20 +796,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1128,7 +1125,7 @@
     <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" customWidth="1"/>
     <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.85546875" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="16.7109375" customWidth="1"/>
@@ -1150,28 +1147,28 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>218</v>
       </c>
       <c r="M1" t="s">
         <v>215</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>217</v>
       </c>
     </row>
@@ -1278,12 +1275,9 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J4" s="7">
-        <v>1.76</v>
-      </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>1760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1349,12 +1343,12 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J6" s="7">
-        <v>1.4</v>
+      <c r="J6" s="6">
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1420,7 +1414,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="K8">
@@ -1457,7 +1451,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>1.18</v>
       </c>
       <c r="K9">
@@ -1494,7 +1488,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>1.42</v>
       </c>
       <c r="K10">
@@ -1565,7 +1559,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>1.42</v>
       </c>
       <c r="K12">
@@ -1636,7 +1630,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="6">
         <v>1.42</v>
       </c>
       <c r="K14">
@@ -1707,12 +1701,9 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J16" s="7">
-        <v>1.46</v>
-      </c>
       <c r="K16">
         <f t="shared" si="1"/>
-        <v>1460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1744,7 +1735,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="6">
         <v>1.18</v>
       </c>
       <c r="K17">
@@ -1883,12 +1874,12 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J21" s="7">
-        <v>1.7</v>
+      <c r="J21" s="6">
+        <v>0</v>
       </c>
       <c r="K21">
         <f t="shared" si="1"/>
-        <v>1700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1920,7 +1911,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="6">
         <v>1.86</v>
       </c>
       <c r="K22">
@@ -1957,7 +1948,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="6">
         <v>1.55</v>
       </c>
       <c r="K23">
@@ -1994,7 +1985,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="6">
         <v>1.4</v>
       </c>
       <c r="K24">
@@ -2065,7 +2056,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="6">
         <v>1.73</v>
       </c>
       <c r="K26">
@@ -2102,7 +2093,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="6">
         <v>2</v>
       </c>
       <c r="K27">
@@ -2377,7 +2368,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="6">
         <v>1.41</v>
       </c>
       <c r="K35">
@@ -2414,7 +2405,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J36" s="7">
+      <c r="J36" s="6">
         <v>3.1</v>
       </c>
       <c r="K36">
@@ -2451,7 +2442,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J37" s="7">
+      <c r="J37" s="6">
         <v>3.5</v>
       </c>
       <c r="K37">
@@ -2522,7 +2513,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J39" s="7">
+      <c r="J39" s="6">
         <v>1.61</v>
       </c>
       <c r="K39">
@@ -2729,7 +2720,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J45" s="7">
+      <c r="J45" s="6">
         <v>1.61</v>
       </c>
       <c r="K45">
@@ -2766,7 +2757,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J46" s="7">
+      <c r="J46" s="6">
         <v>1.63</v>
       </c>
       <c r="K46">
@@ -3041,7 +3032,7 @@
         <f t="shared" si="0"/>
         <v>Away</v>
       </c>
-      <c r="J54" s="7">
+      <c r="J54" s="6">
         <v>1.8</v>
       </c>
       <c r="K54">
@@ -3078,7 +3069,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J55" s="7">
+      <c r="J55" s="6">
         <v>1.85</v>
       </c>
       <c r="K55">
@@ -3183,7 +3174,7 @@
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J58" s="7">
+      <c r="J58" s="6">
         <v>2.15</v>
       </c>
       <c r="K58">
@@ -3260,17 +3251,17 @@
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K61" s="8">
+      <c r="K61" s="7">
         <f>+SUM(K2:K60)</f>
-        <v>41240</v>
-      </c>
-      <c r="L61" s="8">
+        <v>34920</v>
+      </c>
+      <c r="L61" s="7">
         <f>COUNT(J2:J60)*N2</f>
-        <v>24000</v>
-      </c>
-      <c r="M61" s="9">
+        <v>22000</v>
+      </c>
+      <c r="M61" s="8">
         <f>+K61-L61</f>
-        <v>17240</v>
+        <v>12920</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">

--- a/Dia1.xlsx
+++ b/Dia1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alpf0069\Documents\Proyectos\Area TI\Fichas Tecnicas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3068F007-06A7-4CBE-842B-C59244131199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD685E9-ACA1-41C2-898B-AEA57AAA1834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="220">
   <si>
     <t>Home</t>
   </si>
@@ -206,15 +206,6 @@
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
-    <t>Qingdao Youth Island</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
     <t>LNZ Cherkasy</t>
   </si>
   <si>
@@ -699,14 +690,18 @@
   </si>
   <si>
     <t>Beneficios</t>
+  </si>
+  <si>
+    <t>WIN/DRAW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -743,7 +738,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -753,6 +748,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -796,7 +797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -812,6 +813,12 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1115,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -1129,6 +1136,7 @@
     <col min="11" max="11" width="17.85546875" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="15" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1148,28 +1156,31 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="M1" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="M1" t="s">
-        <v>215</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1205,6 +1216,9 @@
         <f>+J2*$N$2</f>
         <v>0</v>
       </c>
+      <c r="L2" s="10">
+        <v>1.8</v>
+      </c>
       <c r="M2" s="2">
         <v>0.5</v>
       </c>
@@ -1238,13 +1252,14 @@
         <v>0.25</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I60" si="0">IF(F3&gt;=$M$2,"Home",IF(G3&gt;=$M$2,"Away",IF(H3&gt;=$M$2,"Draw","")))</f>
+        <f t="shared" ref="I3:I59" si="0">IF(F3&gt;=$M$2,"Home",IF(G3&gt;=$M$2,"Away",IF(H3&gt;=$M$2,"Draw","")))</f>
         <v/>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K60" si="1">+J3*$N$2</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="K3:K59" si="1">+J3*$N$2</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1279,6 +1294,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1313,6 +1329,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1350,6 +1367,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1384,6 +1402,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1421,6 +1440,7 @@
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1458,6 +1478,7 @@
         <f t="shared" si="1"/>
         <v>1180</v>
       </c>
+      <c r="L9" s="10"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1495,6 +1516,7 @@
         <f t="shared" si="1"/>
         <v>1420</v>
       </c>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1529,6 +1551,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1566,6 +1589,7 @@
         <f t="shared" si="1"/>
         <v>1420</v>
       </c>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1600,6 +1624,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1637,6 +1662,7 @@
         <f t="shared" si="1"/>
         <v>1420</v>
       </c>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1671,6 +1697,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1680,200 +1707,208 @@
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="0"/>
+        <v>Away</v>
+      </c>
+      <c r="J16" s="6">
+        <v>1.18</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>1180</v>
+      </c>
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="2">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v>Away</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I21" t="str">
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="I17" t="str">
-        <f t="shared" si="0"/>
-        <v>Away</v>
-      </c>
-      <c r="J17" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I21" t="str">
-        <f t="shared" si="0"/>
-        <v>Away</v>
-      </c>
       <c r="J21" s="6">
         <v>0</v>
       </c>
@@ -1881,8 +1916,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -1890,164 +1926,168 @@
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="G22" s="2">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H22" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
       <c r="J22" s="6">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <f t="shared" si="1"/>
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="L22" s="11"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
         <v>86</v>
       </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v>Home</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="11"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="H23" s="2">
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="2">
         <v>0.2</v>
       </c>
-      <c r="I23" t="str">
-        <f t="shared" si="0"/>
-        <v>Home</v>
-      </c>
-      <c r="J23" s="6">
-        <v>1.55</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="2">
+      <c r="G25" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v>Away</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1.73</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>1730</v>
+      </c>
+      <c r="L25" s="10"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G26" s="2">
         <v>0.55000000000000004</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I24" t="str">
-        <f t="shared" si="0"/>
-        <v>Home</v>
-      </c>
-      <c r="J24" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="1"/>
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.6</v>
       </c>
       <c r="H26" s="2">
         <v>0.2</v>
@@ -2057,140 +2097,141 @@
         <v>Away</v>
       </c>
       <c r="J26" s="6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <f t="shared" si="1"/>
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
         <v>101</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>102</v>
       </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>82</v>
-      </c>
-      <c r="E27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="0"/>
-        <v>Away</v>
-      </c>
-      <c r="J27" s="6">
-        <v>2</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>103</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>104</v>
       </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F28" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="2">
         <v>0.35</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H29" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G30" s="2">
         <v>0.4</v>
       </c>
-      <c r="H28" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I29" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0.35</v>
-      </c>
       <c r="H30" s="2">
         <v>0.25</v>
       </c>
@@ -2202,8 +2243,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="10"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -2211,317 +2253,332 @@
         <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="10"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G32" s="2">
         <v>0.35</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H32" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="0"/>
+        <v>Away</v>
+      </c>
+      <c r="J34" s="6">
+        <v>1.41</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>1410</v>
+      </c>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="0"/>
+        <v>Away</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="10"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="0"/>
+        <v>Home</v>
+      </c>
+      <c r="J36" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G37" s="2">
         <v>0.4</v>
       </c>
-      <c r="H31" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I31" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I32" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="H37" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="10"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" t="s">
         <v>121</v>
       </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G33" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="H33" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" t="s">
-        <v>124</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="H34" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>127</v>
-      </c>
-      <c r="B35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" t="s">
-        <v>124</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="G35" s="2">
+      <c r="F38" s="2">
         <v>0.5</v>
       </c>
-      <c r="H35" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I35" t="str">
-        <f t="shared" si="0"/>
-        <v>Away</v>
-      </c>
-      <c r="J35" s="6">
-        <v>1.41</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="1"/>
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G36" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="I36" t="str">
-        <f t="shared" si="0"/>
-        <v>Away</v>
-      </c>
-      <c r="J36" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="1"/>
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>131</v>
-      </c>
-      <c r="B37" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I37" t="str">
+      <c r="G38" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I38" t="str">
         <f t="shared" si="0"/>
         <v>Home</v>
       </c>
-      <c r="J37" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="1"/>
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>133</v>
-      </c>
-      <c r="B38" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" t="s">
-        <v>124</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="G38" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="H38" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I38" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="J38" s="6">
+        <v>1.61</v>
       </c>
       <c r="K38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1610</v>
+      </c>
+      <c r="L38" s="10"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="D39" t="s">
         <v>138</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F39" s="2">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G39" s="2">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H39" s="2">
         <v>0.25</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="0"/>
-        <v>Home</v>
-      </c>
-      <c r="J39" s="6">
-        <v>1.61</v>
+        <v/>
       </c>
       <c r="K39">
         <f t="shared" si="1"/>
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10"/>
+      <c r="N39">
+        <v>42</v>
+      </c>
+      <c r="O39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2529,90 +2586,100 @@
         <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="F40" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="O40">
+        <f>100/N39</f>
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="P40" s="12">
+        <f>100-(O40*O39)</f>
+        <v>80.952380952380949</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G41" s="2">
         <v>0.45</v>
       </c>
-      <c r="G40" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" t="s">
-        <v>143</v>
-      </c>
-      <c r="C41" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="H41" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="10"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" t="s">
+        <v>148</v>
+      </c>
+      <c r="F42" s="2">
         <v>0.35</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I41" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K41">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" t="s">
-        <v>149</v>
-      </c>
-      <c r="D42" t="s">
-        <v>150</v>
-      </c>
-      <c r="E42" t="s">
-        <v>151</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0.3</v>
       </c>
       <c r="G42" s="2">
         <v>0.45</v>
       </c>
       <c r="H42" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I42" t="str">
         <f t="shared" si="0"/>
@@ -2622,31 +2689,32 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" s="10"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="s">
         <v>152</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" t="s">
-        <v>93</v>
-      </c>
       <c r="E43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F43" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G43" s="2">
         <v>0.35</v>
       </c>
-      <c r="G43" s="2">
-        <v>0.45</v>
-      </c>
       <c r="H43" s="2">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I43" t="str">
         <f t="shared" si="0"/>
@@ -2656,8 +2724,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" s="10"/>
+      <c r="N43">
+        <v>10000</v>
+      </c>
+      <c r="O43">
+        <f>+N43*(N39+O39)</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>154</v>
       </c>
@@ -2665,33 +2741,37 @@
         <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" t="s">
         <v>156</v>
       </c>
-      <c r="E44" t="s">
-        <v>151</v>
-      </c>
       <c r="F44" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G44" s="2">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H44" s="2">
         <v>0.25</v>
       </c>
       <c r="I44" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Home</v>
+      </c>
+      <c r="J44" s="6">
+        <v>0</v>
       </c>
       <c r="K44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>157</v>
       </c>
@@ -2699,36 +2779,49 @@
         <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="D45" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="E45" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F45" s="2">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G45" s="2">
-        <v>0.25</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H45" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I45" t="str">
         <f t="shared" si="0"/>
-        <v>Home</v>
+        <v>Away</v>
       </c>
       <c r="J45" s="6">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="K45">
         <f t="shared" si="1"/>
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1630</v>
+      </c>
+      <c r="L45" s="10"/>
+      <c r="N45">
+        <f>+N43*N39</f>
+        <v>420000</v>
+      </c>
+      <c r="O45">
+        <f>+N45*0.3</f>
+        <v>126000</v>
+      </c>
+      <c r="P45">
+        <f>+N45+O45</f>
+        <v>546000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>160</v>
       </c>
@@ -2739,54 +2832,52 @@
         <v>162</v>
       </c>
       <c r="D46" t="s">
+        <v>163</v>
+      </c>
+      <c r="E46" t="s">
         <v>156</v>
       </c>
-      <c r="E46" t="s">
-        <v>159</v>
-      </c>
       <c r="F46" s="2">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G46" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="H46" s="2">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I46" t="str">
         <f t="shared" si="0"/>
-        <v>Away</v>
-      </c>
-      <c r="J46" s="6">
-        <v>1.63</v>
+        <v/>
       </c>
       <c r="K46">
         <f t="shared" si="1"/>
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="L46" s="10"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="E47" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F47" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G47" s="2">
         <v>0.4</v>
       </c>
-      <c r="G47" s="2">
-        <v>0.35</v>
-      </c>
       <c r="H47" s="2">
         <v>0.25</v>
       </c>
@@ -2798,28 +2889,37 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L47" s="11"/>
+      <c r="N47">
+        <f>100/O43</f>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="O47" s="12">
+        <f>(P45-O43)*N47</f>
+        <v>9.2000000000000011</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" t="s">
         <v>167</v>
       </c>
-      <c r="B48" t="s">
-        <v>168</v>
-      </c>
-      <c r="C48" t="s">
-        <v>169</v>
-      </c>
-      <c r="D48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" t="s">
-        <v>170</v>
-      </c>
       <c r="F48" s="2">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G48" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H48" s="2">
         <v>0.25</v>
@@ -2832,28 +2932,29 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L48" s="10"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D49" t="s">
         <v>174</v>
       </c>
       <c r="E49" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F49" s="2">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="G49" s="2">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H49" s="2">
         <v>0.25</v>
@@ -2866,6 +2967,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L49" s="10"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -2875,20 +2977,20 @@
         <v>176</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="E50" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F50" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G50" s="2">
         <v>0.4</v>
       </c>
-      <c r="G50" s="2">
-        <v>0.35</v>
-      </c>
       <c r="H50" s="2">
         <v>0.25</v>
       </c>
@@ -2900,28 +3002,29 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L50" s="10"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>177</v>
+      </c>
+      <c r="B51" t="s">
         <v>178</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>179</v>
       </c>
-      <c r="C51" t="s">
-        <v>111</v>
-      </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="E51" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F51" s="2">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G51" s="2">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H51" s="2">
         <v>0.25</v>
@@ -2934,28 +3037,29 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L51" s="10"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F52" s="2">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G52" s="2">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="H52" s="2">
         <v>0.25</v>
@@ -2971,133 +3075,133 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>186</v>
+      </c>
+      <c r="B53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
         <v>185</v>
       </c>
-      <c r="B53" t="s">
-        <v>186</v>
-      </c>
-      <c r="C53" t="s">
-        <v>187</v>
-      </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" t="s">
-        <v>188</v>
-      </c>
       <c r="F53" s="2">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="G53" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H53" s="2">
         <v>0.25</v>
       </c>
       <c r="I53" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Away</v>
+      </c>
+      <c r="J53" s="6">
+        <v>1.8</v>
       </c>
       <c r="K53">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" t="s">
         <v>189</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>190</v>
       </c>
-      <c r="C54" t="s">
-        <v>144</v>
-      </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="E54" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F54" s="2">
-        <v>0.25</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G54" s="2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H54" s="2">
         <v>0.25</v>
       </c>
       <c r="I54" t="str">
         <f t="shared" si="0"/>
-        <v>Away</v>
+        <v>Home</v>
       </c>
       <c r="J54" s="6">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="K54">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E55" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F55" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G55" s="2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H55" s="2">
         <v>0.25</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="0"/>
-        <v>Home</v>
-      </c>
-      <c r="J55" s="6">
-        <v>1.85</v>
+        <v/>
       </c>
       <c r="K55">
         <f t="shared" si="1"/>
-        <v>1850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="E56" t="s">
         <v>200</v>
       </c>
       <c r="F56" s="2">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="G56" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H56" s="2">
         <v>0.25</v>
@@ -3119,30 +3223,33 @@
         <v>202</v>
       </c>
       <c r="C57" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F57" s="2">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="G57" s="2">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H57" s="2">
         <v>0.25</v>
       </c>
       <c r="I57" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Home</v>
+      </c>
+      <c r="J57" s="6">
+        <v>2.15</v>
       </c>
       <c r="K57">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -3153,56 +3260,53 @@
         <v>205</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="D58" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F58" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G58" s="2">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="H58" s="2">
         <v>0.25</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="0"/>
-        <v>Home</v>
-      </c>
-      <c r="J58" s="6">
-        <v>2.15</v>
+        <v/>
       </c>
       <c r="K58">
         <f t="shared" si="1"/>
-        <v>2150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>206</v>
+      </c>
+      <c r="B59" t="s">
         <v>207</v>
       </c>
-      <c r="B59" t="s">
-        <v>208</v>
-      </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F59" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G59" s="2">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="H59" s="2">
         <v>0.25</v>
@@ -3217,62 +3321,28 @@
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>209</v>
-      </c>
-      <c r="B60" t="s">
-        <v>210</v>
-      </c>
-      <c r="C60" t="s">
-        <v>144</v>
-      </c>
-      <c r="D60" t="s">
-        <v>177</v>
-      </c>
-      <c r="E60" t="s">
-        <v>203</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K60">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="K60" s="7">
+        <f>+SUM(K2:K59)</f>
+        <v>23400</v>
+      </c>
+      <c r="L60" s="7">
+        <f>COUNT(J2:J59)*N2</f>
+        <v>22000</v>
+      </c>
+      <c r="M60" s="8">
+        <f>+K60-L60</f>
+        <v>1400</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K61" s="7">
-        <f>+SUM(K2:K60)</f>
-        <v>34920</v>
-      </c>
-      <c r="L61" s="7">
-        <f>COUNT(J2:J60)*N2</f>
-        <v>22000</v>
-      </c>
-      <c r="M61" s="8">
-        <f>+K61-L61</f>
-        <v>12920</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K62" t="s">
-        <v>219</v>
-      </c>
-      <c r="L62" t="s">
-        <v>220</v>
-      </c>
-      <c r="M62" t="s">
-        <v>221</v>
+      <c r="K61" t="s">
+        <v>216</v>
+      </c>
+      <c r="L61" t="s">
+        <v>217</v>
+      </c>
+      <c r="M61" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
